--- a/面试/新建 Microsoft Excel 工作表.xlsx
+++ b/面试/新建 Microsoft Excel 工作表.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZQAQ\Desktop\面试\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D9554A-7B0A-41C5-9266-D116C5D63FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4035" yWindow="690" windowWidth="16995" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="15670" windowHeight="8050"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -28,86 +30,69 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>企业</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>投递时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>投递官网</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>腾讯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://join.qq.com/progress.html</t>
   </si>
   <si>
     <t>腾讯音乐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>https://join.tencentmusic.com/deliver</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://join.qq.com/progress.html</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小红书</t>
   </si>
   <si>
     <t>https://job.xiaohongshu.com/campus/record</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小红书</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>美团</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://zhaopin.meituan.com/web/position/detail?jobUnionId=4213684352&amp;highlightType=campus</t>
   </si>
   <si>
     <t>字节</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>https://zhaopin.meituan.com/web/position/detail?jobUnionId=4213684352&amp;highlightType=campus</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>字节跳动校园招聘</t>
   </si>
   <si>
     <t>阿里</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>阿里巴巴校园招聘</t>
   </si>
   <si>
     <t>影石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>移动端开发实习生-UP计划 - 加入影石创新科技股份有限公司</t>
   </si>
   <si>
-    <t>字节跳动校园招聘</t>
-  </si>
-  <si>
     <t>快手</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>快手校招 - 职位详情</t>
   </si>
   <si>
     <t>京东</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>京东校招</t>
   </si>
   <si>
     <t>拼多多</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>拼多多集团-PDD校园招聘官网</t>
@@ -116,40 +101,376 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="10"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -157,27 +478,310 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -226,7 +830,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -261,7 +865,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -435,24 +1039,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
-    <col min="3" max="3" width="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,7 +1062,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -471,101 +1070,101 @@
         <v>3.22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>3.22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>3.22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{EAE0FF95-0E55-47F7-AB6B-389CFA083BB1}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{64D8BBC4-B245-4B2B-968C-5368E43C2B21}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{720284EE-0DE5-4598-941A-E44878A30F93}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{35667B4E-631F-4D5B-A451-98BBDACF967F}"/>
-    <hyperlink ref="C7" r:id="rId5" display="https://campus-talent.alibaba.com/campus/position?batchId=100000540002&amp;filterParams=%7B%22customDept%22%3A%5B%22YKCNU1%22%2C%22O1BGLD%22%2C%222OAHS3%22%2C%22R4NF3G%22%2C%22UXLZSO%22%2C%22FZAWD2%22%2C%221J4ZDE%22%2C%22ISF5EF%22%2C%22GT6VEB%22%2C%22VPZR2I%22%2C%22IU58EO%22%2C%22TOJKBE%22%2C%2282HV2J%22%2C%22Y948F9%22%2C%229ZXLJA%22%2C%22LWEPZA%22%2C%22FNXWXJ%22%2C%22FAIKKZ%22%2C%22T8B7EB%22%2C%22KZ3MMU%22%2C%22PV2VJW%22%2C%22SVOKFU%22%2C%22XUYVTV%22%2C%22C7JZI6%22%2C%223AAN8G%22%2C%22ST33QY%22%2C%22WMREYL%22%2C%22VKQ50F%22%2C%224SF7YD%22%2C%22JQR1WH%22%2C%22CXAHKM%22%2C%22W9ALSO%22%2C%22PHC42X%22%2C%220NZ8T6%22%2C%22JOQMU5%22%2C%22AT1LW3%22%2C%2223DWTR%22%2C%229SQM5Z%22%2C%22GR41YI%22%2C%22O3UD6G%22%2C%22JM3EV0%22%2C%225YTU0N%22%2C%22M0ALLT%22%2C%22VFRMM3%22%2C%22PIOLW3%22%2C%22S9O4SA%22%2C%227EYTIH%22%2C%22WPLY3R%22%2C%2201BJXE%22%2C%22N1AHM4%22%2C%22RMGN6L%22%2C%22MNYQ2O%22%2C%229433MD%22%2C%22Q5EOVE%22%2C%22XE28F9%22%2C%22YZ8741%22%2C%2253MICY%22%2C%22IDN1B2%22%2C%22JVT8G8%22%2C%22N6XDI8%22%2C%22PQHNXW%22%2C%22GT90UP%22%2C%22H8XNGX%22%2C%227UL46E%22%2C%224KHBYK%22%2C%227695L4%22%2C%220PUXGE%22%2C%229FKBXX%22%2C%222HYX5I%22%2C%22P6159J%22%2C%22CORMMP%22%2C%221RTYZS%22%2C%22MVRD2P%22%2C%22IRJJYL%22%2C%22DQMXUA%22%2C%22Z3LCXO%22%2C%22L38HG1%22%2C%22SO65OM%22%2C%223FUOB4%22%2C%22YQNHYU%22%5D%7D" xr:uid="{CB99A52B-02D9-4369-8C57-69E8B355D3D2}"/>
-    <hyperlink ref="C8" r:id="rId6" display="https://arashivision.jobs.feishu.cn/campus/position/7618506036098189578/detail" xr:uid="{B2324344-AB6A-46CF-85B9-63531507F335}"/>
-    <hyperlink ref="C6" r:id="rId7" display="https://jobs.bytedance.com/campus/position?keywords=%E5%AE%A2%E6%88%B7%E7%AB%AF%E5%BC%80%E5%8F%91&amp;category=&amp;location=&amp;project=7194661126919358757&amp;type=&amp;job_hot_flag=&amp;current=1&amp;limit=10&amp;functionCategory=&amp;tag=" xr:uid="{DFFDD91B-6C79-4299-B71C-CEB6B37700D2}"/>
-    <hyperlink ref="C9" r:id="rId8" location="/campus/job-info/11434" display="https://campus.kuaishou.cn/recruit/campus/e/ - /campus/job-info/11434" xr:uid="{7322F257-3668-458B-B321-8C862CBCF9FC}"/>
-    <hyperlink ref="C10" r:id="rId9" location="/details?id=4870" display="https://campus.jd.com/ - /details?id=4870" xr:uid="{964B9414-B7BA-412E-953C-30900F60A5F0}"/>
-    <hyperlink ref="C11" r:id="rId10" display="https://careers.pddglobalhr.com/campus/intern/detail?positionId=093ddc5f-6a57-437d-83ee-fe7a84a1a848" xr:uid="{05F1D04F-0BFF-404A-B855-0434D5D673C6}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://join.tencentmusic.com/deliver"/>
+    <hyperlink ref="C2" r:id="rId2" display="https://join.qq.com/progress.html"/>
+    <hyperlink ref="C4" r:id="rId3" display="https://job.xiaohongshu.com/campus/record"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://zhaopin.meituan.com/web/position/detail?jobUnionId=4213684352&amp;highlightType=campus"/>
+    <hyperlink ref="C7" r:id="rId5" display="阿里巴巴校园招聘"/>
+    <hyperlink ref="C8" r:id="rId6" display="移动端开发实习生-UP计划 - 加入影石创新科技股份有限公司"/>
+    <hyperlink ref="C6" r:id="rId7" display="字节跳动校园招聘"/>
+    <hyperlink ref="C9" r:id="rId8" location="/campus/job-info/11434" display="快手校招 - 职位详情"/>
+    <hyperlink ref="C10" r:id="rId9" location="/details?id=4870" display="京东校招"/>
+    <hyperlink ref="C11" r:id="rId10" display="拼多多集团-PDD校园招聘官网"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/面试/新建 Microsoft Excel 工作表.xlsx
+++ b/面试/新建 Microsoft Excel 工作表.xlsx
@@ -1,19 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Android\gitskills\面试\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B94FEB-1B03-4830-A9A6-9332965885F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4785" yWindow="1860" windowWidth="16995" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="9420" windowHeight="5570" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="72">
   <si>
     <t>企业</t>
   </si>
@@ -105,129 +100,164 @@
   </si>
   <si>
     <t>唯品会</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>唯品会（中国）有限公司 - 校园招聘</t>
   </si>
   <si>
+    <t>百度</t>
+  </si>
+  <si>
     <t>百度校园招聘</t>
   </si>
   <si>
-    <t>百度</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>B站</t>
   </si>
   <si>
     <t>哔哩哔哩-招聘</t>
   </si>
   <si>
-    <t>B站</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>欢聚</t>
   </si>
   <si>
     <t>欢聚集团招聘官网</t>
   </si>
   <si>
-    <t>欢聚</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>小米</t>
   </si>
   <si>
     <t>小米实习生招聘</t>
   </si>
   <si>
-    <t>小米</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>oppo</t>
   </si>
   <si>
     <t>OPPO招聘 - 加入我们 join us - 岗位详情</t>
   </si>
   <si>
-    <t>oppo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>vivo</t>
   </si>
   <si>
     <t>vivo招聘</t>
   </si>
   <si>
-    <t>vivo</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>科大讯飞</t>
   </si>
   <si>
     <t>科大讯飞 | 校园招聘官网</t>
   </si>
   <si>
-    <t>科大讯飞</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>联想</t>
   </si>
   <si>
     <t>岗位详情</t>
   </si>
   <si>
-    <t>联想</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>中兴</t>
   </si>
   <si>
     <t>中兴通讯 - 校园招聘</t>
   </si>
   <si>
-    <t>中兴</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>小马</t>
   </si>
   <si>
     <t>实习研发工程师 - 工程/算法 - 小马智行校园招聘</t>
   </si>
   <si>
-    <t>小马</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>cvte</t>
   </si>
   <si>
     <t>CVTE校招门户- 应用软件工程师</t>
   </si>
   <si>
-    <t>cvte</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>37互娱</t>
   </si>
   <si>
     <t>三七互娱 - 校园招聘</t>
   </si>
   <si>
+    <t>云智研</t>
+  </si>
+  <si>
     <t>云智研发公司 - 校园招聘</t>
   </si>
   <si>
-    <t>37互娱</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>云智研</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>阅文集团</t>
   </si>
   <si>
     <t>实习招聘</t>
   </si>
   <si>
-    <t>阅文集团</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>荣耀</t>
   </si>
   <si>
     <t>荣耀招聘|招聘官网</t>
   </si>
   <si>
-    <t>荣耀</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>minimax</t>
   </si>
   <si>
     <t>Agent 客户端开发实习生（AI Agent / AI App） - 加入MiniMax</t>
   </si>
   <si>
-    <t>minimax</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>得物</t>
+  </si>
+  <si>
+    <t>得物App校园招聘</t>
+  </si>
+  <si>
+    <t>研究生学业奖学金</t>
+  </si>
+  <si>
+    <t>一等奖</t>
+  </si>
+  <si>
+    <t>蓝桥杯编程大赛</t>
+  </si>
+  <si>
+    <t>广东省二等奖</t>
+  </si>
+  <si>
+    <t>二等奖</t>
+  </si>
+  <si>
+    <t>本科学业奖学金</t>
+  </si>
+  <si>
+    <t>三等奖</t>
+  </si>
+  <si>
+    <t>全国大学生数学建模大赛</t>
+  </si>
+  <si>
+    <t>广东省一等奖</t>
+  </si>
+  <si>
+    <t>全国大学生数学竞赛</t>
+  </si>
+  <si>
+    <t>广东省三等奖</t>
+  </si>
+  <si>
+    <t>全国大学生大数据分析技术技能大赛</t>
+  </si>
+  <si>
+    <t>全国二等奖</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="5">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +274,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -252,30 +289,337 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -283,29 +627,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -563,19 +1189,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -586,51 +1212,51 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="C2" s="1" t="s">
+        <v>4.9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="C3" s="1" t="s">
+        <v>4.9</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="C4" s="1" t="s">
+        <v>4.9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -638,7 +1264,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -646,40 +1272,40 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -687,173 +1313,342 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="B12">
+        <v>4.9</v>
+      </c>
       <c r="C12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:3">
       <c r="A17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:3">
       <c r="A20" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:3">
       <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:3">
       <c r="A22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:3">
       <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+      <c r="B25" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:3">
       <c r="A26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:3">
       <c r="A27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:3">
       <c r="A28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>55</v>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="1">
+        <v>4.1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="C7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="C8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="C6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="C9" r:id="rId8" location="/campus/job-info/11434" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="C10" r:id="rId9" location="/details?id=4870" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="C11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="C12" r:id="rId11" location="/job/722c21ab-645d-4a48-b357-a17df2c5b503" display="https://app-tc.mokahr.com/campus-recruitment/vipshophr/8015?sourceToken=d7b00ea2471aaddd55b3f402bb4fcc19 - /job/722c21ab-645d-4a48-b357-a17df2c5b503" xr:uid="{100A8CAC-F8A4-4B94-A73F-F48CE50601AB}"/>
-    <hyperlink ref="C13" r:id="rId12" display="https://talent.baidu.com/jobs/list" xr:uid="{80EFF7EA-31A9-455E-8769-E55949D61E12}"/>
-    <hyperlink ref="C14" r:id="rId13" display="https://jobs.bilibili.com/campus/positions/27006" xr:uid="{9C7F0C24-5106-495F-BDE2-A7C22FE08C69}"/>
-    <hyperlink ref="C15" r:id="rId14" location="/job/b933394c-11d7-4222-93cb-107edd291cf3" display="https://hr.joyy.com/apply/hjsd/48 - /job/b933394c-11d7-4222-93cb-107edd291cf3" xr:uid="{6C1EE3E7-76FB-418D-865F-F59FA286FE55}"/>
-    <hyperlink ref="C16" r:id="rId15" display="https://xiaomi.jobs.f.mioffice.cn/internship/?keywords=%E5%AE%A2%E6%88%B7%E7%AB%AF&amp;category=&amp;location=&amp;project=&amp;type=&amp;job_hot_flag=&amp;current=1&amp;limit=10&amp;functionCategory=&amp;tag=&amp;spread=6AA3R7B" xr:uid="{A128345C-92E5-486F-98EE-8F6BCA424C58}"/>
-    <hyperlink ref="C17" r:id="rId16" display="https://careers.oppo.com/university/oppo/campus/post/1648?recruitType=Intern" xr:uid="{8EE77162-3507-431B-975B-B0EEE85D1EB9}"/>
-    <hyperlink ref="C18" r:id="rId17" display="https://hr-campus.vivo.com/intern/detail?jobAdId=af12baa9-0fb2-45b6-b137-ac27b785cbfd" xr:uid="{37450737-FD51-44EB-84E8-3C7EBA9E99F6}"/>
-    <hyperlink ref="C19" r:id="rId18" display="https://iflytek.zhiye.com/intern/detail?jobAdId=7333ff5d-2208-408c-b612-aff4dc6b44b3" xr:uid="{17318C8E-53E0-4722-9CE9-BBBD1EA20B86}"/>
-    <hyperlink ref="C20" r:id="rId19" display="https://talent.lenovo.com.cn/position/detail?id=1931" xr:uid="{E868E713-3E02-4339-9406-317AB4D721A8}"/>
-    <hyperlink ref="C21" r:id="rId20" location="/job/aab4ae4e-4ac1-40f5-b078-645f87005c64" display="https://app.mokahr.com/campus-recruitment/zte/46903 - /job/aab4ae4e-4ac1-40f5-b078-645f87005c64" xr:uid="{3C5EA0FE-797A-48B8-9636-73EDD4BAD6FC}"/>
-    <hyperlink ref="C22" r:id="rId21" display="https://ponyai.jobs.feishu.cn/ponycampus/position/7470411605089552659/detail" xr:uid="{DC85DF95-D357-4177-AC9D-2CE7DB5B20B3}"/>
-    <hyperlink ref="C23" r:id="rId22" display="https://campus.cvte.com/position/a722c588fec44f50ba24eb129b301f07" xr:uid="{FDC99940-944C-4C76-AEDC-A8D7E94EFF3F}"/>
-    <hyperlink ref="C24" r:id="rId23" location="/job/e4bfb146-7e13-4928-a844-3adafcc72164" display="https://app.mokahr.com/campus-recruitment/37/58016?locale=zh-CN - /job/e4bfb146-7e13-4928-a844-3adafcc72164" xr:uid="{C2DD8E9A-9B9A-432E-96DB-71604834A0C7}"/>
-    <hyperlink ref="C25" r:id="rId24" location="/job/2c40ac19-bfa2-404d-9a48-8b1f682349bb" display="https://app-tc.mokahr.com/campus-recruitment/csig/20001 - /job/2c40ac19-bfa2-404d-9a48-8b1f682349bb" xr:uid="{4C8392BA-D280-474D-8C60-3A987AC64268}"/>
-    <hyperlink ref="C26" r:id="rId25" display="https://join.yuewen.com/fieldwork" xr:uid="{82C0C9FA-349A-4093-9739-7E8DC71DA1EF}"/>
-    <hyperlink ref="C27" r:id="rId26" display="https://career.honor.com/SU61b9b9992f9d24431f5050a5/pb/posDetail.html?postId=69ce09c2abe720345e419f77&amp;postType=intern" xr:uid="{0C3E85D8-5F6A-4134-9ED9-091916753CD5}"/>
-    <hyperlink ref="C28" r:id="rId27" display="https://vrfi1sk8a0.jobs.feishu.cn/379481/position/7535804843156736299/detail" xr:uid="{BD40F835-B65C-4C15-A693-C56284A0E08A}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://join.tencentmusic.com/deliver"/>
+    <hyperlink ref="C2" r:id="rId2" display="https://join.qq.com/progress.html"/>
+    <hyperlink ref="C4" r:id="rId3" display="https://job.xiaohongshu.com/campus/record"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://zhaopin.meituan.com/web/position/detail?jobUnionId=4213684352&amp;highlightType=campus"/>
+    <hyperlink ref="C7" r:id="rId5" display="阿里巴巴校园招聘"/>
+    <hyperlink ref="C8" r:id="rId6" display="移动端开发实习生-UP计划 - 加入影石创新科技股份有限公司"/>
+    <hyperlink ref="C6" r:id="rId7" display="字节跳动校园招聘"/>
+    <hyperlink ref="C9" r:id="rId8" location="/campus/job-info/11434" display="快手校招 - 职位详情"/>
+    <hyperlink ref="C10" r:id="rId9" location="/details?id=4870" display="京东校招"/>
+    <hyperlink ref="C11" r:id="rId10" display="拼多多集团-PDD校园招聘官网"/>
+    <hyperlink ref="C12" r:id="rId11" location="/job/722c21ab-645d-4a48-b357-a17df2c5b503" display="唯品会（中国）有限公司 - 校园招聘"/>
+    <hyperlink ref="C13" r:id="rId12" display="百度校园招聘"/>
+    <hyperlink ref="C14" r:id="rId13" display="哔哩哔哩-招聘"/>
+    <hyperlink ref="C15" r:id="rId14" location="/job/b933394c-11d7-4222-93cb-107edd291cf3" display="欢聚集团招聘官网"/>
+    <hyperlink ref="C16" r:id="rId15" display="小米实习生招聘"/>
+    <hyperlink ref="C17" r:id="rId16" display="OPPO招聘 - 加入我们 join us - 岗位详情"/>
+    <hyperlink ref="C18" r:id="rId17" display="vivo招聘"/>
+    <hyperlink ref="C19" r:id="rId18" display="科大讯飞 | 校园招聘官网"/>
+    <hyperlink ref="C20" r:id="rId19" display="岗位详情"/>
+    <hyperlink ref="C21" r:id="rId20" location="/job/aab4ae4e-4ac1-40f5-b078-645f87005c64" display="中兴通讯 - 校园招聘"/>
+    <hyperlink ref="C22" r:id="rId21" display="实习研发工程师 - 工程/算法 - 小马智行校园招聘"/>
+    <hyperlink ref="C23" r:id="rId22" display="CVTE校招门户- 应用软件工程师"/>
+    <hyperlink ref="C24" r:id="rId23" location="/job/e4bfb146-7e13-4928-a844-3adafcc72164" display="三七互娱 - 校园招聘"/>
+    <hyperlink ref="C25" r:id="rId24" location="/job/2c40ac19-bfa2-404d-9a48-8b1f682349bb" display="云智研发公司 - 校园招聘"/>
+    <hyperlink ref="C26" r:id="rId25" display="实习招聘"/>
+    <hyperlink ref="C27" r:id="rId26" display="荣耀招聘|招聘官网"/>
+    <hyperlink ref="C28" r:id="rId27" display="Agent 客户端开发实习生（AI Agent / AI App） - 加入MiniMax"/>
+    <hyperlink ref="C29" r:id="rId28" display="得物App校园招聘" tooltip="https://poizon.jobs.feishu.cn/578078/?spread=M9XXNCV"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="23" customWidth="1"/>
+    <col min="2" max="2" width="12.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1">
+        <v>2025.09</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3">
+        <v>2024.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4">
+        <v>2023.09</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5">
+        <v>2022.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>2021.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2022.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="1">
+        <v>2022.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C9">
+        <v>2022.11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/面试/新建 Microsoft Excel 工作表.xlsx
+++ b/面试/新建 Microsoft Excel 工作表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Android\gitskills\面试\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0B94FEB-1B03-4830-A9A6-9332965885F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A0825D1-8877-4E15-8A11-CB8F4D5FD884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4785" yWindow="1860" windowWidth="16995" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -691,6 +691,9 @@
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="B12">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="C12" s="2" t="s">
         <v>24</v>
       </c>

--- a/面试/新建 Microsoft Excel 工作表.xlsx
+++ b/面试/新建 Microsoft Excel 工作表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Android\gitskills\面试\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC34E7E-6763-4410-8532-46C3B9B1EB9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="9420" windowHeight="5570" activeTab="1"/>
+    <workbookView xWindow="4980" yWindow="3375" windowWidth="16995" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -249,15 +255,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,337 +291,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -627,311 +314,29 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1189,19 +594,19 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1212,100 +617,104 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
       <c r="B3">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>9</v>
       </c>
       <c r="B5">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
+      <c r="B6" s="1">
+        <v>4.0999999999999996</v>
+      </c>
       <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
+      <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
       <c r="B9">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1313,18 +722,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B12">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>25</v>
       </c>
@@ -1332,84 +741,84 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
@@ -1417,73 +826,73 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>45</v>
       </c>
       <c r="B23" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>47</v>
       </c>
       <c r="B24" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>49</v>
       </c>
       <c r="B25" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>51</v>
       </c>
       <c r="B26" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>53</v>
       </c>
       <c r="B27" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>55</v>
       </c>
@@ -1491,64 +900,63 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>57</v>
       </c>
       <c r="B29" s="1">
-        <v>4.1</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="C29" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://join.tencentmusic.com/deliver"/>
-    <hyperlink ref="C2" r:id="rId2" display="https://join.qq.com/progress.html"/>
-    <hyperlink ref="C4" r:id="rId3" display="https://job.xiaohongshu.com/campus/record"/>
-    <hyperlink ref="C5" r:id="rId4" display="https://zhaopin.meituan.com/web/position/detail?jobUnionId=4213684352&amp;highlightType=campus"/>
-    <hyperlink ref="C7" r:id="rId5" display="阿里巴巴校园招聘"/>
-    <hyperlink ref="C8" r:id="rId6" display="移动端开发实习生-UP计划 - 加入影石创新科技股份有限公司"/>
-    <hyperlink ref="C6" r:id="rId7" display="字节跳动校园招聘"/>
-    <hyperlink ref="C9" r:id="rId8" location="/campus/job-info/11434" display="快手校招 - 职位详情"/>
-    <hyperlink ref="C10" r:id="rId9" location="/details?id=4870" display="京东校招"/>
-    <hyperlink ref="C11" r:id="rId10" display="拼多多集团-PDD校园招聘官网"/>
-    <hyperlink ref="C12" r:id="rId11" location="/job/722c21ab-645d-4a48-b357-a17df2c5b503" display="唯品会（中国）有限公司 - 校园招聘"/>
-    <hyperlink ref="C13" r:id="rId12" display="百度校园招聘"/>
-    <hyperlink ref="C14" r:id="rId13" display="哔哩哔哩-招聘"/>
-    <hyperlink ref="C15" r:id="rId14" location="/job/b933394c-11d7-4222-93cb-107edd291cf3" display="欢聚集团招聘官网"/>
-    <hyperlink ref="C16" r:id="rId15" display="小米实习生招聘"/>
-    <hyperlink ref="C17" r:id="rId16" display="OPPO招聘 - 加入我们 join us - 岗位详情"/>
-    <hyperlink ref="C18" r:id="rId17" display="vivo招聘"/>
-    <hyperlink ref="C19" r:id="rId18" display="科大讯飞 | 校园招聘官网"/>
-    <hyperlink ref="C20" r:id="rId19" display="岗位详情"/>
-    <hyperlink ref="C21" r:id="rId20" location="/job/aab4ae4e-4ac1-40f5-b078-645f87005c64" display="中兴通讯 - 校园招聘"/>
-    <hyperlink ref="C22" r:id="rId21" display="实习研发工程师 - 工程/算法 - 小马智行校园招聘"/>
-    <hyperlink ref="C23" r:id="rId22" display="CVTE校招门户- 应用软件工程师"/>
-    <hyperlink ref="C24" r:id="rId23" location="/job/e4bfb146-7e13-4928-a844-3adafcc72164" display="三七互娱 - 校园招聘"/>
-    <hyperlink ref="C25" r:id="rId24" location="/job/2c40ac19-bfa2-404d-9a48-8b1f682349bb" display="云智研发公司 - 校园招聘"/>
-    <hyperlink ref="C26" r:id="rId25" display="实习招聘"/>
-    <hyperlink ref="C27" r:id="rId26" display="荣耀招聘|招聘官网"/>
-    <hyperlink ref="C28" r:id="rId27" display="Agent 客户端开发实习生（AI Agent / AI App） - 加入MiniMax"/>
-    <hyperlink ref="C29" r:id="rId28" display="得物App校园招聘" tooltip="https://poizon.jobs.feishu.cn/578078/?spread=M9XXNCV"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="C4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="C6" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="C9" r:id="rId8" location="/campus/job-info/11434" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="C10" r:id="rId9" location="/details?id=4870" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="C12" r:id="rId11" location="/job/722c21ab-645d-4a48-b357-a17df2c5b503" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="C15" r:id="rId14" location="/job/b933394c-11d7-4222-93cb-107edd291cf3" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="C16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="C17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="C18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="C19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="C20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="C21" r:id="rId20" location="/job/aab4ae4e-4ac1-40f5-b078-645f87005c64" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="C22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="C23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="C24" r:id="rId23" location="/job/e4bfb146-7e13-4928-a844-3adafcc72164" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="C25" r:id="rId24" location="/job/2c40ac19-bfa2-404d-9a48-8b1f682349bb" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="C26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="C28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="C29" r:id="rId28" tooltip="https://poizon.jobs.feishu.cn/578078/?spread=M9XXNCV" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="12.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>59</v>
       </c>
@@ -1559,7 +967,7 @@
         <v>2025.09</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>61</v>
       </c>
@@ -1570,7 +978,7 @@
         <v>2025.06</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>59</v>
       </c>
@@ -1581,7 +989,7 @@
         <v>2024.09</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>64</v>
       </c>
@@ -1592,7 +1000,7 @@
         <v>2023.09</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>64</v>
       </c>
@@ -1603,7 +1011,7 @@
         <v>2022.09</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1614,7 +1022,7 @@
         <v>2021.09</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>66</v>
       </c>
@@ -1625,7 +1033,7 @@
         <v>2022.1</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -1636,7 +1044,7 @@
         <v>2022.1</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -1648,7 +1056,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>